--- a/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
@@ -89879,13 +89879,13 @@
         <v>8</v>
       </c>
       <c r="AX410" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY410" t="n">
         <v>14</v>
       </c>
       <c r="AZ410" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA410" t="n">
         <v>2</v>
@@ -90760,13 +90760,13 @@
         <v>16</v>
       </c>
       <c r="BA414" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB414" t="n">
         <v>6</v>
       </c>
       <c r="BC414" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD414" t="n">
         <v>2.65</v>
@@ -90978,13 +90978,13 @@
         <v>8</v>
       </c>
       <c r="BA415" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB415" t="n">
         <v>2</v>
       </c>
       <c r="BC415" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD415" t="n">
         <v>2.23</v>
@@ -91184,13 +91184,13 @@
         <v>3</v>
       </c>
       <c r="AW416" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX416" t="n">
         <v>9</v>
       </c>
       <c r="AY416" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ416" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
@@ -90088,7 +90088,7 @@
         <v>3.02</v>
       </c>
       <c r="AU411" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV411" t="n">
         <v>2</v>
@@ -90100,7 +90100,7 @@
         <v>0</v>
       </c>
       <c r="AY411" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ411" t="n">
         <v>2</v>
@@ -91399,13 +91399,13 @@
         <v>2</v>
       </c>
       <c r="AV417" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW417" t="n">
         <v>4</v>
       </c>
       <c r="AX417" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY417" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP418"/>
+  <dimension ref="A1:BP419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.38</v>
@@ -5492,7 +5492,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -7018,7 +7018,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR30" t="n">
         <v>1.42</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.78</v>
@@ -11596,7 +11596,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR51" t="n">
         <v>0.9</v>
@@ -14427,7 +14427,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.82</v>
@@ -17700,7 +17700,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR79" t="n">
         <v>1.91</v>
@@ -19005,7 +19005,7 @@
         <v>1.33</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.41</v>
@@ -22496,7 +22496,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR101" t="n">
         <v>1.73</v>
@@ -26199,7 +26199,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.88</v>
@@ -29254,7 +29254,7 @@
         <v>0.22</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR132" t="n">
         <v>1.13</v>
@@ -33611,7 +33611,7 @@
         <v>1.2</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ152" t="n">
         <v>1</v>
@@ -34050,7 +34050,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR154" t="n">
         <v>1.81</v>
@@ -34704,7 +34704,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR157" t="n">
         <v>1.77</v>
@@ -35791,7 +35791,7 @@
         <v>2</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.71</v>
@@ -41026,7 +41026,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR186" t="n">
         <v>1.64</v>
@@ -41459,7 +41459,7 @@
         <v>1.13</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.44</v>
@@ -47563,7 +47563,7 @@
         <v>0.75</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ216" t="n">
         <v>1.12</v>
@@ -48002,7 +48002,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR218" t="n">
         <v>1.25</v>
@@ -51054,7 +51054,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR232" t="n">
         <v>1.5</v>
@@ -54103,7 +54103,7 @@
         <v>0.9</v>
       </c>
       <c r="AP246" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ246" t="n">
         <v>0.89</v>
@@ -56504,7 +56504,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ257" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR257" t="n">
         <v>1.49</v>
@@ -58027,7 +58027,7 @@
         <v>1.7</v>
       </c>
       <c r="AP264" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ264" t="n">
         <v>1.59</v>
@@ -63041,7 +63041,7 @@
         <v>1</v>
       </c>
       <c r="AP287" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ287" t="n">
         <v>1.28</v>
@@ -64134,7 +64134,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ292" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR292" t="n">
         <v>1.3</v>
@@ -66093,7 +66093,7 @@
         <v>1.77</v>
       </c>
       <c r="AP301" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ301" t="n">
         <v>1.61</v>
@@ -67840,7 +67840,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ309" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR309" t="n">
         <v>1.73</v>
@@ -72854,7 +72854,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ332" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR332" t="n">
         <v>1.41</v>
@@ -74159,7 +74159,7 @@
         <v>1.43</v>
       </c>
       <c r="AP338" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ338" t="n">
         <v>1.22</v>
@@ -80045,7 +80045,7 @@
         <v>1.07</v>
       </c>
       <c r="AP365" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ365" t="n">
         <v>1</v>
@@ -81356,7 +81356,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ371" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR371" t="n">
         <v>1.77</v>
@@ -82007,7 +82007,7 @@
         <v>0.63</v>
       </c>
       <c r="AP374" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AQ374" t="n">
         <v>0.61</v>
@@ -83536,7 +83536,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ381" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AR381" t="n">
         <v>2.03</v>
@@ -91678,6 +91678,224 @@
       </c>
       <c r="BP418" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="n">
+        <v>8202176</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="n">
+        <v>46083.70833333334</v>
+      </c>
+      <c r="F419" t="n">
+        <v>35</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Birmingham City</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>0</v>
+      </c>
+      <c r="J419" t="n">
+        <v>2</v>
+      </c>
+      <c r="K419" t="n">
+        <v>2</v>
+      </c>
+      <c r="L419" t="n">
+        <v>1</v>
+      </c>
+      <c r="M419" t="n">
+        <v>3</v>
+      </c>
+      <c r="N419" t="n">
+        <v>4</v>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>['13', '26', '60']</t>
+        </is>
+      </c>
+      <c r="Q419" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R419" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S419" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T419" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U419" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V419" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="W419" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X419" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="Y419" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z419" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA419" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AB419" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC419" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD419" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE419" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF419" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG419" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH419" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AI419" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ419" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK419" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL419" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM419" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN419" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO419" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AP419" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ419" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR419" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS419" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT419" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AU419" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV419" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW419" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX419" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY419" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ419" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA419" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB419" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC419" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD419" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE419" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF419" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG419" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH419" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI419" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ419" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK419" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL419" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM419" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BN419" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO419" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BP419" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP419"/>
+  <dimension ref="A1:BP420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.28</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.59</v>
@@ -11160,7 +11160,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR49" t="n">
         <v>1.32</v>
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.22</v>
@@ -12686,7 +12686,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR56" t="n">
         <v>1.28</v>
@@ -18133,7 +18133,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ81" t="n">
         <v>1</v>
@@ -18354,7 +18354,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR82" t="n">
         <v>1.37</v>
@@ -24019,7 +24019,7 @@
         <v>2</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.44</v>
@@ -26202,7 +26202,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR118" t="n">
         <v>1.76</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.89</v>
@@ -29687,7 +29687,7 @@
         <v>1.5</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.61</v>
@@ -32742,7 +32742,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR148" t="n">
         <v>1.48</v>
@@ -35358,7 +35358,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR160" t="n">
         <v>1.21</v>
@@ -35573,7 +35573,7 @@
         <v>0.33</v>
       </c>
       <c r="AP161" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.12</v>
@@ -41241,7 +41241,7 @@
         <v>1.29</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.59</v>
@@ -41898,7 +41898,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR190" t="n">
         <v>1.6</v>
@@ -45604,7 +45604,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR207" t="n">
         <v>1.48</v>
@@ -49307,7 +49307,7 @@
         <v>2.22</v>
       </c>
       <c r="AP224" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.61</v>
@@ -51923,7 +51923,7 @@
         <v>1.4</v>
       </c>
       <c r="AP236" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ236" t="n">
         <v>1.22</v>
@@ -53670,7 +53670,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR244" t="n">
         <v>1.6</v>
@@ -57155,7 +57155,7 @@
         <v>0.78</v>
       </c>
       <c r="AP260" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ260" t="n">
         <v>0.41</v>
@@ -60210,7 +60210,7 @@
         <v>0.22</v>
       </c>
       <c r="AQ274" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR274" t="n">
         <v>1.19</v>
@@ -62390,7 +62390,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ284" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR284" t="n">
         <v>1.45</v>
@@ -65439,7 +65439,7 @@
         <v>0.75</v>
       </c>
       <c r="AP298" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ298" t="n">
         <v>0.78</v>
@@ -68491,7 +68491,7 @@
         <v>1.5</v>
       </c>
       <c r="AP312" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ312" t="n">
         <v>1.24</v>
@@ -69584,7 +69584,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ317" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR317" t="n">
         <v>1.73</v>
@@ -71543,7 +71543,7 @@
         <v>1.46</v>
       </c>
       <c r="AP326" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ326" t="n">
         <v>1.47</v>
@@ -71982,7 +71982,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ328" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR328" t="n">
         <v>1.33</v>
@@ -76993,7 +76993,7 @@
         <v>1.43</v>
       </c>
       <c r="AP351" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ351" t="n">
         <v>1.29</v>
@@ -77650,7 +77650,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ354" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR354" t="n">
         <v>1.4</v>
@@ -90076,7 +90076,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ411" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AR411" t="n">
         <v>1.67</v>
@@ -90509,7 +90509,7 @@
         <v>0.88</v>
       </c>
       <c r="AP413" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AQ413" t="n">
         <v>0.82</v>
@@ -91896,6 +91896,224 @@
       </c>
       <c r="BP419" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="n">
+        <v>8202133</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F420" t="n">
+        <v>32</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>0</v>
+      </c>
+      <c r="J420" t="n">
+        <v>0</v>
+      </c>
+      <c r="K420" t="n">
+        <v>0</v>
+      </c>
+      <c r="L420" t="n">
+        <v>1</v>
+      </c>
+      <c r="M420" t="n">
+        <v>0</v>
+      </c>
+      <c r="N420" t="n">
+        <v>1</v>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q420" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R420" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S420" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="T420" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U420" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V420" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W420" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X420" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y420" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA420" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB420" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC420" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD420" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE420" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF420" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG420" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH420" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AI420" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ420" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK420" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AL420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM420" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AN420" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO420" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP420" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AQ420" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR420" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS420" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT420" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AU420" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW420" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX420" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY420" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ420" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA420" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB420" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC420" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD420" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BE420" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF420" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BG420" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH420" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI420" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ420" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BK420" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL420" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BM420" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN420" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO420" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP420" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
@@ -93582,13 +93582,13 @@
         <v>1</v>
       </c>
       <c r="AW427" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX427" t="n">
         <v>6</v>
       </c>
       <c r="AY427" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ427" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England Championship_20252026.xlsx
@@ -93149,13 +93149,13 @@
         <v>19</v>
       </c>
       <c r="AX425" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY425" t="n">
         <v>23</v>
       </c>
       <c r="AZ425" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA425" t="n">
         <v>12</v>
